--- a/authorization_forms/041_student_ministry_medical_and_photo_release_form--authorization_forms.xlsx
+++ b/authorization_forms/041_student_ministry_medical_and_photo_release_form--authorization_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'parent',_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Parent', 'value': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'guardian',_'value':_'guardian'}</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Guardian', 'value': 'Guardian'}</t>
+          <t>Guardian</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other_contact',_'value':_'other_contact'}</t>
+          <t>other_contact</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other Contact', 'value': 'Other Contact'}</t>
+          <t>Other Contact</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'parent_and_child',_'value':_'parent_and_child'}</t>
+          <t>parent_and_child</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Parent and Child', 'value': 'Parent and Child'}</t>
+          <t>Parent and Child</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'parent',_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Parent', 'value': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'ministry',_'value':_'ministry'}</t>
+          <t>ministry</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Ministry', 'value': 'Ministry'}</t>
+          <t>Ministry</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'church',_'value':_'church'}</t>
+          <t>church</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Church', 'value': 'Church'}</t>
+          <t>Church</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'camp',_'value':_'camp'}</t>
+          <t>camp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Camp', 'value': 'Camp'}</t>
+          <t>Camp</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'retreat',_'value':_'retreat'}</t>
+          <t>retreat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Retreat', 'value': 'Retreat'}</t>
+          <t>Retreat</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'event',_'value':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Event', 'value': 'Event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
